--- a/excel/monsters.xlsx
+++ b/excel/monsters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GODOT\Project\BOOOM202604\Booom202604\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D112249F-B639-4298-8FAB-99137860B2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E700D09D-BA00-4CF8-B1D8-F96EA3805F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="368" yWindow="368" windowWidth="19965" windowHeight="15119" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>ID</t>
   </si>
@@ -45,13 +45,7 @@
     <t>穴居杂兵靠蛮力扑咬。</t>
   </si>
   <si>
-    <t>res://Art/Icon/monster.png</t>
-  </si>
-  <si>
     <t>废墟里晃动的巨大骨架力量惊人。</t>
-  </si>
-  <si>
-    <t>res://Art/Icon/ruins.png</t>
   </si>
   <si>
     <r>
@@ -190,7 +184,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>res://Art/Icon/ruins.png</t>
+    <t>res://Art/monsterIcon/2001.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/monsterIcon/2002.png</t>
+  </si>
+  <si>
+    <t>res://Art/monsterIcon/3001.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/monsterIcon/3002.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/monsterIcon/4001.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/monsterIcon/4002.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -574,7 +587,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -588,7 +601,7 @@
         <v>2001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
@@ -600,7 +613,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.65" x14ac:dyDescent="0.45">
@@ -608,10 +621,10 @@
         <v>2002</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -620,7 +633,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.65" x14ac:dyDescent="0.45">
@@ -628,10 +641,10 @@
         <v>3001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -640,7 +653,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.65" x14ac:dyDescent="0.45">
@@ -648,10 +661,10 @@
         <v>3002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -660,7 +673,7 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="14.65" x14ac:dyDescent="0.45">
@@ -668,10 +681,10 @@
         <v>4001</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -680,7 +693,7 @@
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.65" x14ac:dyDescent="0.45">
@@ -688,10 +701,10 @@
         <v>4002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -700,7 +713,7 @@
         <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
